--- a/SLR/Full-Paper-Read/Paper-Review/PS16.xlsx
+++ b/SLR/Full-Paper-Read/Paper-Review/PS16.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="58">
   <si>
     <t>ID</t>
   </si>
@@ -26,7 +26,7 @@
     <t>The paper proposes the following contributions:</t>
   </si>
   <si>
-    <t xml:space="preserve">The paper introduces a Real-time Linked Dataspace (RLD) as an enabling platform for data management within smart environments. This paper identifies common data management requirements for smart energy and water environments, details the RLD architecture and the key support services and their tiered support levels, and a principled approach to ‘‘Pay-As-You-Go’’ data management. The paper presents a dataspace query service for real-time data streams and entities to enable unified entity-centric queries across live and historical stream data. </t>
+    <t>The paper presents a Cloud-based approach with a Dynamic Domain Name System (DDNS) mechanism enabling the IoT devices to communicate using the Representational state transfer (REST) model: an approach that follows the Web of things (WoT) paradigm. In particular, the system makes the IoT devices’ hosted resources (e.g., sensors and actuators) able to be steered using globally resolvable (over the Internet) Uniform Resource Locators (URLs) even when deployed behind Network Address Translators (NATs) and firewalls.</t>
   </si>
   <si>
     <t>&lt;add your comment here if any&gt;</t>
@@ -35,7 +35,7 @@
     <t>CPS Case Study / Example availability</t>
   </si>
   <si>
-    <t>Five pilots for smart energy and water management systems in smart buildings: Smart Airport, Smart Office, Smart Homes, Mixed Use, Smart School</t>
+    <t>Online accessible testbed powered by the S4T DDNS system. felooca.eu not accessible</t>
   </si>
   <si>
     <t>SECO Tools Availability (add repository or website in the comment)</t>
@@ -44,46 +44,40 @@
     <t>N</t>
   </si>
   <si>
+    <t>https://github.com/MDSLab/wstun</t>
+  </si>
+  <si>
     <t>Related Challenge - See SPE paper (Write Others in comment cell)</t>
   </si>
   <si>
-    <t>Data</t>
-  </si>
-  <si>
-    <t>Requirements engineering</t>
-  </si>
-  <si>
-    <t>Intelligence and automation</t>
+    <t>Others</t>
   </si>
   <si>
     <t>n.a.</t>
   </si>
   <si>
+    <t>interoperability issues in IoT</t>
+  </si>
+  <si>
     <t>Does it contribute to answer RQ1?</t>
   </si>
   <si>
-    <t>Not during the CPS development, but challenges in data management in smart environments</t>
-  </si>
-  <si>
     <t>Does the paper present methods, tools, and benefits in terms of industry/academia collaboration? If so, write what methods, tools, and benefits in the comment column</t>
   </si>
   <si>
-    <t>No mention of industry-academia collaboration.</t>
+    <t>No mention of industry-academia collaboration</t>
   </si>
   <si>
     <t>Does it contribute to answer RQ2?</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>Application Domain(s) (at least one or domain independent)</t>
   </si>
   <si>
-    <t>Others</t>
-  </si>
-  <si>
-    <t>Smart energy and water management systems</t>
+    <t>Application Domain Independent</t>
+  </si>
+  <si>
+    <t>IoT networks and environments</t>
   </si>
   <si>
     <t>Quality Evaluation (From 1 to 10) - From "Quality" Tab</t>
@@ -198,7 +192,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -224,6 +218,13 @@
       <name val="Arial"/>
     </font>
     <font/>
+    <font>
+      <i/>
+      <u/>
+      <sz val="10.0"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+    </font>
     <font>
       <sz val="12.0"/>
       <color theme="1"/>
@@ -562,7 +563,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -598,36 +599,33 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="17" fillId="5" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="18" fillId="5" fontId="5" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="16" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="18" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="19" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="20" fillId="4" fontId="1" numFmtId="1" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="18" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="16" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="19" fillId="5" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
     <xf borderId="18" fillId="5" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="16" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="18" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="19" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="20" fillId="4" fontId="1" numFmtId="1" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="18" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="16" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="19" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="19" fillId="5" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="18" fillId="5" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
     <xf borderId="21" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
@@ -637,78 +635,84 @@
     <xf borderId="18" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="22" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="22" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="23" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="23" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="24" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf borderId="25" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="24" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf borderId="25" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="25" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="24" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="26" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="24" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="24" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="25" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="26" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="24" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf borderId="25" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="25" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="25" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="24" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="24" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf borderId="25" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="25" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="25" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="24" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="24" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf borderId="25" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="25" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="25" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1025,7 +1029,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="17">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="18"/>
@@ -1052,7 +1056,7 @@
       <c r="G5" s="18"/>
       <c r="H5" s="18"/>
       <c r="I5" s="21" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -1060,28 +1064,28 @@
         <v>4.0</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="D6" s="22" t="s">
         <v>13</v>
       </c>
+      <c r="E6" s="22" t="s">
+        <v>13</v>
+      </c>
       <c r="F6" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="23" t="s">
         <v>14</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="23" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
@@ -1100,7 +1104,7 @@
       <c r="G7" s="25"/>
       <c r="H7" s="18"/>
       <c r="I7" s="26" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -1108,9 +1112,9 @@
         <v>6.0</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="25"/>
@@ -1118,8 +1122,8 @@
       <c r="F8" s="25"/>
       <c r="G8" s="25"/>
       <c r="H8" s="18"/>
-      <c r="I8" s="26" t="s">
-        <v>18</v>
+      <c r="I8" s="23" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
@@ -1127,9 +1131,9 @@
         <v>7.0</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="28" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="25"/>
@@ -1137,8 +1141,8 @@
       <c r="F9" s="25"/>
       <c r="G9" s="25"/>
       <c r="H9" s="18"/>
-      <c r="I9" s="30" t="s">
-        <v>20</v>
+      <c r="I9" s="29" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -1146,28 +1150,28 @@
         <v>8.0</v>
       </c>
       <c r="B10" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="23" t="s">
         <v>21</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" s="26" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
@@ -1175,30 +1179,30 @@
         <v>9.0</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="33">
+        <v>22</v>
+      </c>
+      <c r="C11" s="32">
         <f>Quality!C29</f>
-        <v>8.703703704</v>
+        <v>8.333333333</v>
       </c>
       <c r="D11" s="25"/>
       <c r="E11" s="25"/>
       <c r="F11" s="25"/>
       <c r="G11" s="25"/>
       <c r="H11" s="25"/>
-      <c r="I11" s="21" t="s">
+      <c r="I11" s="29" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1"/>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="B14" s="34" t="s">
-        <v>25</v>
+      <c r="B14" s="33" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="B15" s="34" t="s">
-        <v>26</v>
+      <c r="B15" s="33" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1"/>
@@ -2235,10 +2239,13 @@
       <formula1>"n.a.,Y,N"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="I5"/>
+  </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2257,83 +2264,83 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="35"/>
-      <c r="B1" s="36" t="s">
+      <c r="A1" s="34"/>
+      <c r="B1" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="36"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="38"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="B2" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="37"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="39"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="40" t="s">
+      <c r="C2" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="42"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="43"/>
+      <c r="B3" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="C3" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="D3" s="36"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="42"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="43"/>
+      <c r="B4" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="42">
+      <c r="C4" s="41">
         <v>1.0</v>
       </c>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="43"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="44"/>
-      <c r="B3" s="41" t="s">
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="43"/>
+      <c r="B5" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="42">
+      <c r="C5" s="41">
         <v>1.0</v>
       </c>
-      <c r="D3" s="37"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="43"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="44"/>
-      <c r="B4" s="41" t="s">
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="43"/>
+      <c r="B6" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="44"/>
-      <c r="B5" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="44"/>
-      <c r="B6" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
+      <c r="C6" s="44">
+        <v>0.5</v>
+      </c>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
     </row>
     <row r="7">
       <c r="A7" s="45"/>
-      <c r="B7" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="42">
-        <v>1.0</v>
+      <c r="B7" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="44">
+        <v>0.5</v>
       </c>
       <c r="D7" s="46">
         <f>COUNTIF(B2:B7,"&lt;&gt;text")</f>
@@ -2341,136 +2348,136 @@
       </c>
       <c r="E7" s="46">
         <f>(SUM(C2:C7)/D7)*10</f>
-        <v>10</v>
+        <v>8.333333333</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="47" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B8" s="48" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C8" s="49">
         <v>1.0</v>
       </c>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
     </row>
     <row r="9">
-      <c r="A9" s="44"/>
+      <c r="A9" s="43"/>
       <c r="B9" s="48" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="49">
-        <v>1.0</v>
-      </c>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
+        <v>36</v>
+      </c>
+      <c r="C9" s="50">
+        <v>0.5</v>
+      </c>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
     </row>
     <row r="10">
-      <c r="A10" s="44"/>
+      <c r="A10" s="43"/>
       <c r="B10" s="48" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C10" s="49">
         <v>1.0</v>
       </c>
-      <c r="D10" s="37"/>
-      <c r="E10" s="37"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
     </row>
     <row r="11">
-      <c r="A11" s="44"/>
+      <c r="A11" s="43"/>
       <c r="B11" s="48" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C11" s="50">
         <v>0.5</v>
       </c>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
     </row>
     <row r="12">
-      <c r="A12" s="44"/>
+      <c r="A12" s="43"/>
       <c r="B12" s="48" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C12" s="49">
         <v>1.0</v>
       </c>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
     </row>
     <row r="13">
-      <c r="A13" s="44"/>
+      <c r="A13" s="43"/>
       <c r="B13" s="48" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C13" s="49">
         <v>1.0</v>
       </c>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
     </row>
     <row r="14">
-      <c r="A14" s="44"/>
+      <c r="A14" s="43"/>
       <c r="B14" s="48" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C14" s="49">
         <v>1.0</v>
       </c>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
     </row>
     <row r="15">
-      <c r="A15" s="44"/>
+      <c r="A15" s="43"/>
       <c r="B15" s="48" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C15" s="50">
         <v>0.5</v>
       </c>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
     </row>
     <row r="16">
-      <c r="A16" s="44"/>
+      <c r="A16" s="43"/>
       <c r="B16" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="50">
-        <v>0.5</v>
-      </c>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
+        <v>43</v>
+      </c>
+      <c r="C16" s="49">
+        <v>1.0</v>
+      </c>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
     </row>
     <row r="17">
-      <c r="A17" s="44"/>
+      <c r="A17" s="43"/>
       <c r="B17" s="48" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C17" s="49">
         <v>1.0</v>
       </c>
-      <c r="D17" s="37"/>
-      <c r="E17" s="37"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
     </row>
     <row r="18">
-      <c r="A18" s="44"/>
+      <c r="A18" s="43"/>
       <c r="B18" s="48" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C18" s="49">
         <v>1.0</v>
       </c>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
     </row>
     <row r="19">
       <c r="A19" s="45"/>
       <c r="B19" s="48" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C19" s="49">
         <v>1.0</v>
@@ -2486,67 +2493,67 @@
     </row>
     <row r="20">
       <c r="A20" s="51" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B20" s="52" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C20" s="53">
         <v>1.0</v>
       </c>
-      <c r="D20" s="37"/>
-      <c r="E20" s="37"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
     </row>
     <row r="21">
-      <c r="A21" s="44"/>
+      <c r="A21" s="43"/>
       <c r="B21" s="52" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C21" s="54">
         <v>0.5</v>
       </c>
-      <c r="D21" s="37"/>
-      <c r="E21" s="37"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
     </row>
     <row r="22">
-      <c r="A22" s="44"/>
+      <c r="A22" s="43"/>
       <c r="B22" s="52" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="54">
+        <v>0.5</v>
+      </c>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="43"/>
+      <c r="B23" s="52" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" s="53">
+        <v>1.0</v>
+      </c>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="42"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="43"/>
+      <c r="B24" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="44"/>
-      <c r="B23" s="52" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" s="54">
+      <c r="C24" s="54">
         <v>0.5</v>
       </c>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="43"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="44"/>
-      <c r="B24" s="52" t="s">
-        <v>54</v>
-      </c>
-      <c r="C24" s="53">
-        <v>1.0</v>
-      </c>
-      <c r="D24" s="38"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="43"/>
+      <c r="D24" s="37"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="42"/>
     </row>
     <row r="25">
       <c r="A25" s="45"/>
       <c r="B25" s="52" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C25" s="53">
         <v>1.0</v>
@@ -2557,43 +2564,43 @@
       </c>
       <c r="E25" s="55">
         <f>(SUM(C20:C25)/D25)*10</f>
-        <v>6.666666667</v>
-      </c>
-      <c r="F25" s="43"/>
+        <v>7.5</v>
+      </c>
+      <c r="F25" s="42"/>
     </row>
     <row r="26">
       <c r="A26" s="56" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B26" s="57" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C26" s="58">
         <v>1.0</v>
       </c>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="43"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="42"/>
     </row>
     <row r="27">
-      <c r="A27" s="44"/>
+      <c r="A27" s="43"/>
       <c r="B27" s="57" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C27" s="58">
         <v>1.0</v>
       </c>
-      <c r="D27" s="38"/>
-      <c r="E27" s="38"/>
-      <c r="F27" s="43"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="42"/>
     </row>
     <row r="28">
       <c r="A28" s="45"/>
       <c r="B28" s="57" t="s">
-        <v>59</v>
-      </c>
-      <c r="C28" s="58">
-        <v>1.0</v>
+        <v>57</v>
+      </c>
+      <c r="C28" s="59">
+        <v>0.5</v>
       </c>
       <c r="D28" s="55">
         <f>COUNTIF(B26:B28,"&lt;&gt;text")</f>
@@ -2601,18 +2608,18 @@
       </c>
       <c r="E28" s="55">
         <f>(SUM(C26:C28)/D28)*10</f>
-        <v>10</v>
-      </c>
-      <c r="F28" s="43"/>
+        <v>8.333333333</v>
+      </c>
+      <c r="F28" s="42"/>
     </row>
     <row r="29">
-      <c r="B29" s="59">
+      <c r="B29" s="60">
         <f>COUNTIF(B2:B28,"&lt;&gt;text")</f>
         <v>27</v>
       </c>
-      <c r="C29" s="59">
+      <c r="C29" s="60">
         <f>(SUM(C2:C28)/B29)*10</f>
-        <v>8.703703704</v>
+        <v>8.333333333</v>
       </c>
     </row>
   </sheetData>
